--- a/data/trans_orig/P04B1_1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>301012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>338276</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>425416</t>
+          <t>421818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>466520</t>
+          <t>465525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>735872</t>
+          <t>736956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>794259</t>
+          <t>793664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175883</t>
+          <t>174538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213932</t>
+          <t>213147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288388</t>
+          <t>289383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329492</t>
+          <t>333090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474807</t>
+          <t>475402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533194</t>
+          <t>532110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1579248</t>
+          <t>1579945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1850997</t>
+          <t>1884932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1510911</t>
+          <t>1509752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1776323</t>
+          <t>1771508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3128098</t>
+          <t>3122710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3546002</t>
+          <t>3513542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437369</t>
+          <t>403434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>709118</t>
+          <t>708421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458812</t>
+          <t>463627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>724224</t>
+          <t>725383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977499</t>
+          <t>1009959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1395403</t>
+          <t>1400791</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448392</t>
+          <t>445686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>495873</t>
+          <t>495500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>469523</t>
+          <t>469894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>507535</t>
+          <t>508594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>931213</t>
+          <t>925018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>991081</t>
+          <t>990191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148373</t>
+          <t>148746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195854</t>
+          <t>198560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148872</t>
+          <t>147813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186884</t>
+          <t>186513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309572</t>
+          <t>310462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369440</t>
+          <t>375635</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2364700</t>
+          <t>2364983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2681396</t>
+          <t>2664092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2434648</t>
+          <t>2434058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2731414</t>
+          <t>2732789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4837241</t>
+          <t>4850964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5271883</t>
+          <t>5291257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>765375</t>
+          <t>782679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1082071</t>
+          <t>1081788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>915035</t>
+          <t>913660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1211801</t>
+          <t>1212391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1821337</t>
+          <t>1801963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2255979</t>
+          <t>2242256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>320627</t>
+          <t>358825</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>301012</t>
+          <t>333733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>339621</t>
+          <t>381052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>445469</t>
+          <t>468592</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>421818</t>
+          <t>445082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465525</t>
+          <t>489471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>766096</t>
+          <t>827417</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>736956</t>
+          <t>793032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>793664</t>
+          <t>861139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>193532</t>
+          <t>218701</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174538</t>
+          <t>196474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213147</t>
+          <t>243793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>309439</t>
+          <t>352799</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289383</t>
+          <t>331920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333090</t>
+          <t>376309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>502970</t>
+          <t>571500</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>475402</t>
+          <t>537778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532110</t>
+          <t>605885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514159</t>
+          <t>577526</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754908</t>
+          <t>821391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754908</t>
+          <t>821391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754908</t>
+          <t>821391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269066</t>
+          <t>1398917</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269066</t>
+          <t>1398917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269066</t>
+          <t>1398917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1669875</t>
+          <t>1502936</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1579945</t>
+          <t>1454501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1884932</t>
+          <t>1554260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1597460</t>
+          <t>1429054</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1509752</t>
+          <t>1388196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1771508</t>
+          <t>1470488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3267335</t>
+          <t>2931990</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3122710</t>
+          <t>2871384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3513542</t>
+          <t>3003600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>618491</t>
+          <t>725545</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403434</t>
+          <t>674221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>708421</t>
+          <t>773980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>637675</t>
+          <t>738854</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463627</t>
+          <t>697420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725383</t>
+          <t>779712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1256166</t>
+          <t>1464398</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009959</t>
+          <t>1392788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1400791</t>
+          <t>1525004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288366</t>
+          <t>2228481</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288366</t>
+          <t>2228481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288366</t>
+          <t>2228481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235135</t>
+          <t>2167908</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235135</t>
+          <t>2167908</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235135</t>
+          <t>2167908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523501</t>
+          <t>4396388</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523501</t>
+          <t>4396388</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523501</t>
+          <t>4396388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>471600</t>
+          <t>512392</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445686</t>
+          <t>485767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>495500</t>
+          <t>536027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>490112</t>
+          <t>534808</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>469894</t>
+          <t>509835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>508594</t>
+          <t>554274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>961712</t>
+          <t>1047200</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>925018</t>
+          <t>1013304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>990191</t>
+          <t>1079599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172646</t>
+          <t>195253</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148746</t>
+          <t>171618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198560</t>
+          <t>221878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166295</t>
+          <t>195113</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147813</t>
+          <t>175647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186513</t>
+          <t>220086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>338941</t>
+          <t>390366</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310462</t>
+          <t>357967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375635</t>
+          <t>424262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644246</t>
+          <t>707645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644246</t>
+          <t>707645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644246</t>
+          <t>707645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>656407</t>
+          <t>729921</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>656407</t>
+          <t>729921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>656407</t>
+          <t>729921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1300653</t>
+          <t>1437566</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1300653</t>
+          <t>1437566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1300653</t>
+          <t>1437566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2462103</t>
+          <t>2374153</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2364983</t>
+          <t>2315668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2664092</t>
+          <t>2429680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2533041</t>
+          <t>2432454</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2434058</t>
+          <t>2382303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2732789</t>
+          <t>2488797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4995143</t>
+          <t>4806607</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4850964</t>
+          <t>4728024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5291257</t>
+          <t>4890937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>984668</t>
+          <t>1139499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>782679</t>
+          <t>1083972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1081788</t>
+          <t>1197984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1113408</t>
+          <t>1286766</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913660</t>
+          <t>1230423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1212391</t>
+          <t>1336917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2098077</t>
+          <t>2426264</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801963</t>
+          <t>2341934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2242256</t>
+          <t>2504847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446771</t>
+          <t>3513652</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446771</t>
+          <t>3513652</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446771</t>
+          <t>3513652</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3646449</t>
+          <t>3719220</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3646449</t>
+          <t>3719220</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3646449</t>
+          <t>3719220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7093220</t>
+          <t>7232871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7093220</t>
+          <t>7232871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7093220</t>
+          <t>7232871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
